--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/DELAWARE_2015.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/DELAWARE_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D515"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -461,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="8">
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Los Cabos</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -505,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="11">
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Palizada</t>
@@ -549,10 +589,15 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -580,10 +625,15 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Amatán</t>
@@ -597,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C17">
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -632,10 +697,15 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -697,10 +787,15 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -749,10 +859,15 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Jiquipilas</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -805,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C33">
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -892,10 +1057,15 @@
         <v>20</v>
       </c>
       <c r="D39">
-        <v>0.009237875288683603</v>
+        <v>0.009237875288683604</v>
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1018,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -1040,10 +1255,15 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1071,10 +1291,15 @@
         <v>2</v>
       </c>
       <c r="D52">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1116,7 +1351,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1171,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C60">
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1210,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1223,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1236,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1249,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1262,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1271,10 +1561,15 @@
         <v>2</v>
       </c>
       <c r="D67">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1284,10 +1579,15 @@
         <v>2</v>
       </c>
       <c r="D68">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1297,10 +1597,15 @@
         <v>2</v>
       </c>
       <c r="D69">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1323,10 +1633,15 @@
         <v>2</v>
       </c>
       <c r="D71">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1371,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1380,10 +1705,15 @@
         <v>2</v>
       </c>
       <c r="D75">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1393,36 +1723,51 @@
         <v>2</v>
       </c>
       <c r="D76">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pánuco de Coronado</t>
+          <t>Pánuco De Coronado</t>
         </is>
       </c>
       <c r="C77">
         <v>2</v>
       </c>
       <c r="D77">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>San Pedro del Gallo</t>
+          <t>San Pedro Del Gallo</t>
         </is>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1438,12 +1783,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C80">
@@ -1454,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Aculco</t>
@@ -1467,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C82">
@@ -1480,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C83">
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Amanalco</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Amecameca</t>
@@ -1528,10 +1903,15 @@
         <v>2</v>
       </c>
       <c r="D86">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Atizapán</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1554,10 +1939,15 @@
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Calimaya</t>
@@ -1584,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1597,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Chicoloapan</t>
@@ -1610,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1619,13 +2029,18 @@
         <v>2</v>
       </c>
       <c r="D93">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Coacalco de Berriozábal</t>
+          <t>Coacalco De Berriozábal</t>
         </is>
       </c>
       <c r="C94">
@@ -1636,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1649,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C96">
@@ -1662,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1675,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Hueypoxtla</t>
@@ -1688,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1701,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C100">
@@ -1714,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ixtapan del Oro</t>
+          <t>Ixtapan Del Oro</t>
         </is>
       </c>
       <c r="C101">
@@ -1727,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1740,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -1749,13 +2209,18 @@
         <v>2</v>
       </c>
       <c r="D103">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C104">
@@ -1766,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1779,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Ocoyoacac</t>
@@ -1788,10 +2263,15 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Ocuilan</t>
@@ -1805,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Otzoloapan</t>
@@ -1818,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Otzolotepec</t>
@@ -1831,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -1844,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C111">
@@ -1857,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>San Martín de las Pirámides</t>
+          <t>San Martín De Las Pirámides</t>
         </is>
       </c>
       <c r="C112">
@@ -1870,19 +2375,29 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>San Simón de Guerrero</t>
+          <t>San Simón De Guerrero</t>
         </is>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Santo Tomás</t>
@@ -1896,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -1909,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1922,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1935,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1944,10 +2479,15 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Temoaya</t>
@@ -1961,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1974,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tenango del Valle</t>
+          <t>Tenango Del Valle</t>
         </is>
       </c>
       <c r="C121">
@@ -1987,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Tequixquiac</t>
@@ -2000,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -2013,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -2026,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Tlalmanalco</t>
@@ -2039,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C126">
@@ -2052,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2065,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -2078,22 +2663,32 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Valle de Bravo</t>
+          <t>Valle De Bravo</t>
         </is>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Valle de Chalco Solidaridad</t>
+          <t>Valle De Chalco Solidaridad</t>
         </is>
       </c>
       <c r="C130">
@@ -2104,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Villa del Carbón</t>
+          <t>Villa Del Carbón</t>
         </is>
       </c>
       <c r="C131">
@@ -2117,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -2130,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Zacualpan</t>
@@ -2143,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Zinacantepec</t>
@@ -2156,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Zumpahuacán</t>
@@ -2169,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2196,10 +2821,15 @@
         <v>2</v>
       </c>
       <c r="D137">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2213,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C139">
@@ -2226,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2239,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -2248,10 +2893,15 @@
         <v>2</v>
       </c>
       <c r="D141">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2265,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2278,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>León</t>
@@ -2291,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -2304,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2317,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2330,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -2343,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2352,13 +3037,18 @@
         <v>2</v>
       </c>
       <c r="D149">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C150">
@@ -2369,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -2382,19 +3077,29 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C152">
         <v>2</v>
       </c>
       <c r="D152">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -2408,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2421,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2441,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C156">
@@ -2452,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -2465,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -2474,13 +3199,18 @@
         <v>2</v>
       </c>
       <c r="D158">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C159">
@@ -2491,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C160">
@@ -2504,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -2517,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C162">
@@ -2530,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C163">
@@ -2543,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -2556,22 +3311,32 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C165">
         <v>2</v>
       </c>
       <c r="D165">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C166">
@@ -2582,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -2595,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Cualác</t>
@@ -2608,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cuetzala del Progreso</t>
+          <t>Cuetzala Del Progreso</t>
         </is>
       </c>
       <c r="C169">
@@ -2621,19 +3401,29 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C170">
         <v>2</v>
       </c>
       <c r="D170">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -2647,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -2660,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C173">
@@ -2673,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Iguala de la Independencia</t>
+          <t>Iguala De La Independencia</t>
         </is>
       </c>
       <c r="C174">
@@ -2686,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -2699,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -2712,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -2725,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C178">
@@ -2738,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -2751,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2764,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -2777,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Pilcaya</t>
@@ -2790,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -2803,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2816,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -2825,13 +3685,18 @@
         <v>2</v>
       </c>
       <c r="D185">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C186">
@@ -2842,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C187">
@@ -2855,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2868,9 +3743,14 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C189">
@@ -2881,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -2894,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Tlacoachistlahuaca</t>
@@ -2907,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -2920,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -2933,19 +3833,29 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C194">
         <v>2</v>
       </c>
       <c r="D194">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -2959,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2986,10 +3901,15 @@
         <v>2</v>
       </c>
       <c r="D197">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Ajacuba</t>
@@ -3003,19 +3923,29 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C199">
         <v>2</v>
       </c>
       <c r="D199">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -3029,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -3042,19 +3977,29 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C202">
         <v>2</v>
       </c>
       <c r="D202">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3068,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -3081,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C205">
@@ -3094,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>San Felipe Orizatlán</t>
@@ -3103,10 +4063,15 @@
         <v>2</v>
       </c>
       <c r="D206">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>San Salvador</t>
@@ -3120,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -3133,19 +4103,29 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C209">
         <v>2</v>
       </c>
       <c r="D209">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Tizayuca</t>
@@ -3159,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -3168,13 +4153,18 @@
         <v>2</v>
       </c>
       <c r="D211">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C212">
@@ -3185,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C213">
@@ -3198,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3218,7 +4218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Acatlán de Juárez</t>
+          <t>Acatlán De Juárez</t>
         </is>
       </c>
       <c r="C215">
@@ -3229,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Atotonilco el Alto</t>
+          <t>Atotonilco El Alto</t>
         </is>
       </c>
       <c r="C216">
@@ -3242,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -3255,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -3264,13 +4279,18 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C219">
@@ -3281,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3294,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -3307,9 +4337,14 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C222">
@@ -3320,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -3333,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -3346,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -3359,19 +4409,29 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>San Martín de Bolaños</t>
+          <t>San Martín De Bolaños</t>
         </is>
       </c>
       <c r="C226">
         <v>2</v>
       </c>
       <c r="D226">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -3385,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -3398,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C229">
@@ -3411,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -3424,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -3437,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -3446,13 +4531,18 @@
         <v>2</v>
       </c>
       <c r="D232">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C233">
@@ -3463,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -3476,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3507,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Angangueo</t>
@@ -3520,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -3533,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -3542,10 +4657,15 @@
         <v>2</v>
       </c>
       <c r="D239">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Arteaga</t>
@@ -3555,10 +4675,15 @@
         <v>2</v>
       </c>
       <c r="D240">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -3572,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Chavinda</t>
@@ -3585,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Coahuayana</t>
@@ -3598,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -3611,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -3624,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -3637,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -3650,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -3659,10 +4819,15 @@
         <v>2</v>
       </c>
       <c r="D248">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -3676,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -3689,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -3702,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -3715,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -3724,10 +4909,15 @@
         <v>2</v>
       </c>
       <c r="D253">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Nahuatzen</t>
@@ -3741,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -3754,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Nuevo Urecho</t>
@@ -3763,10 +4963,15 @@
         <v>2</v>
       </c>
       <c r="D256">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -3776,10 +4981,15 @@
         <v>2</v>
       </c>
       <c r="D257">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -3789,10 +4999,15 @@
         <v>2</v>
       </c>
       <c r="D258">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -3806,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -3819,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -3832,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -3845,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Taretan</t>
@@ -3858,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -3871,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -3884,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -3893,10 +5143,15 @@
         <v>2</v>
       </c>
       <c r="D266">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -3906,10 +5161,15 @@
         <v>2</v>
       </c>
       <c r="D267">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Tzintzuntzan</t>
@@ -3923,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -3936,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -3949,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -3962,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3975,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -3988,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4015,10 +5305,15 @@
         <v>2</v>
       </c>
       <c r="D275">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Axochiapan</t>
@@ -4028,10 +5323,15 @@
         <v>2</v>
       </c>
       <c r="D276">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Ayala</t>
@@ -4045,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -4058,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -4071,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -4080,10 +5395,15 @@
         <v>2</v>
       </c>
       <c r="D280">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Huitzilac</t>
@@ -4097,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -4106,13 +5431,18 @@
         <v>20</v>
       </c>
       <c r="D282">
-        <v>0.009237875288683603</v>
+        <v>0.009237875288683604</v>
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C283">
@@ -4123,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -4136,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -4149,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Tetecala</t>
@@ -4162,9 +5507,14 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C287">
@@ -4175,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -4184,10 +5539,15 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Xochitepec</t>
@@ -4201,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -4214,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -4227,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Zacatepec</t>
@@ -4240,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4267,10 +5647,15 @@
         <v>2</v>
       </c>
       <c r="D294">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -4284,9 +5669,14 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C296">
@@ -4297,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -4310,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -4319,10 +5719,15 @@
         <v>2</v>
       </c>
       <c r="D298">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -4332,10 +5737,15 @@
         <v>2</v>
       </c>
       <c r="D299">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4367,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -4380,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4400,7 +5820,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ayoquezco de Aldama</t>
+          <t>Ayoquezco De Aldama</t>
         </is>
       </c>
       <c r="C304">
@@ -4411,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Candelaria Loxicha</t>
@@ -4420,13 +5845,18 @@
         <v>2</v>
       </c>
       <c r="D305">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C306">
@@ -4437,9 +5867,14 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C307">
@@ -4450,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>La Compañía</t>
@@ -4463,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>La Reforma</t>
@@ -4476,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -4489,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Magdalena Tequisistlán</t>
@@ -4502,9 +5957,14 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C312">
@@ -4515,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -4524,10 +5989,15 @@
         <v>2</v>
       </c>
       <c r="D313">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Mesones Hidalgo</t>
@@ -4541,9 +6011,14 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C315">
@@ -4554,35 +6029,50 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C316">
         <v>2</v>
       </c>
       <c r="D316">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C317">
         <v>2</v>
       </c>
       <c r="D317">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C318">
@@ -4593,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Reyes Etla</t>
@@ -4606,9 +6101,14 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>San Felipe Jalapa de Díaz</t>
+          <t>San Felipe Jalapa De Díaz</t>
         </is>
       </c>
       <c r="C320">
@@ -4619,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -4628,10 +6133,15 @@
         <v>2</v>
       </c>
       <c r="D321">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -4645,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>San Juan Cacahuatepec</t>
@@ -4658,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -4671,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>San Martín Zacatepec</t>
@@ -4684,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -4697,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -4710,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>San Miguel Tlacotepec</t>
@@ -4723,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -4732,10 +6277,15 @@
         <v>2</v>
       </c>
       <c r="D329">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>San Pedro Amuzgos</t>
@@ -4745,10 +6295,15 @@
         <v>2</v>
       </c>
       <c r="D330">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>San Sebastián Abasolo</t>
@@ -4762,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -4771,10 +6331,15 @@
         <v>2</v>
       </c>
       <c r="D332">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -4784,10 +6349,15 @@
         <v>2</v>
       </c>
       <c r="D333">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Santiago Cacaloxtepec</t>
@@ -4801,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Santiago Camotlán</t>
@@ -4814,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -4827,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -4840,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -4853,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Santiago Tamazola</t>
@@ -4862,10 +6457,15 @@
         <v>2</v>
       </c>
       <c r="D339">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -4879,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -4888,23 +6493,33 @@
         <v>2</v>
       </c>
       <c r="D341">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C342">
         <v>2</v>
       </c>
       <c r="D342">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Valerio Trujano</t>
@@ -4918,9 +6533,14 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C344">
@@ -4931,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Zapotitlán Lagunas</t>
@@ -4944,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4971,10 +6601,15 @@
         <v>2</v>
       </c>
       <c r="D347">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -4988,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Ahuehuetitla</t>
@@ -5001,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Ajalpan</t>
@@ -5014,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Aljojuca</t>
@@ -5027,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Atexcal</t>
@@ -5040,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -5053,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -5066,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Chapulco</t>
@@ -5079,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -5092,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -5105,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -5118,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Chilchotla</t>
@@ -5131,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -5140,10 +6835,15 @@
         <v>2</v>
       </c>
       <c r="D360">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -5157,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Cuautlancingo</t>
@@ -5170,9 +6875,14 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Cuetzalan del Progreso</t>
+          <t>Cuetzalan Del Progreso</t>
         </is>
       </c>
       <c r="C363">
@@ -5183,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -5196,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Domingo Arenas</t>
@@ -5209,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -5218,10 +6943,15 @@
         <v>2</v>
       </c>
       <c r="D366">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -5235,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -5248,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -5261,9 +7001,14 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C370">
@@ -5274,19 +7019,29 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Huehuetlán el Grande</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C371">
         <v>2</v>
       </c>
       <c r="D371">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -5300,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -5309,13 +7069,18 @@
         <v>2</v>
       </c>
       <c r="D373">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C374">
@@ -5326,6 +7091,11 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -5339,19 +7109,29 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C376">
         <v>2</v>
       </c>
       <c r="D376">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -5365,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -5378,9 +7163,14 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C379">
@@ -5391,6 +7181,11 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -5404,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -5417,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>San José Miahuatlán</t>
@@ -5430,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -5443,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>San Matías Tlalancaleca</t>
@@ -5456,9 +7271,14 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>San Nicolás de los Ranchos</t>
+          <t>San Nicolás De Los Ranchos</t>
         </is>
       </c>
       <c r="C385">
@@ -5469,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -5482,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>San Pedro Yeloixtlahuaca</t>
@@ -5495,9 +7325,14 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C388">
@@ -5508,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>San Sebastián Tlacotepec</t>
@@ -5521,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -5530,23 +7375,33 @@
         <v>2</v>
       </c>
       <c r="D390">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Tepatlaxco de Hidalgo</t>
+          <t>Tepatlaxco De Hidalgo</t>
         </is>
       </c>
       <c r="C391">
         <v>2</v>
       </c>
       <c r="D391">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -5560,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -5573,9 +7433,14 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C394">
@@ -5586,9 +7451,14 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C395">
@@ -5599,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -5612,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>Tlachichuca</t>
@@ -5625,9 +7505,14 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C398">
@@ -5638,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -5651,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Tlaltenango</t>
@@ -5664,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -5673,10 +7573,15 @@
         <v>2</v>
       </c>
       <c r="D401">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -5690,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -5703,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -5712,10 +7627,15 @@
         <v>2</v>
       </c>
       <c r="D404">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -5729,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -5742,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -5755,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -5764,10 +7699,15 @@
         <v>2</v>
       </c>
       <c r="D408">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Zoquitlán</t>
@@ -5777,10 +7717,15 @@
         <v>2</v>
       </c>
       <c r="D409">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5801,7 +7746,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C411">
@@ -5812,9 +7757,14 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C412">
@@ -5825,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -5834,13 +7789,18 @@
         <v>2</v>
       </c>
       <c r="D413">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C414">
@@ -5851,9 +7811,14 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C415">
@@ -5864,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5895,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5926,9 +7901,14 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C420">
@@ -5939,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -5952,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -5965,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -5978,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -5991,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -6004,9 +8009,14 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C426">
@@ -6017,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6030,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Tamasopo</t>
@@ -6043,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -6056,9 +8081,14 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C430">
@@ -6069,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6100,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -6113,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -6126,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6153,10 +8203,15 @@
         <v>2</v>
       </c>
       <c r="D436">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -6170,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -6183,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6214,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Padilla</t>
@@ -6227,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -6240,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -6253,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6284,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -6297,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -6306,13 +8401,18 @@
         <v>2</v>
       </c>
       <c r="D447">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Nanacamilpa de Mariano Arista</t>
+          <t>Nanacamilpa De Mariano Arista</t>
         </is>
       </c>
       <c r="C448">
@@ -6323,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -6336,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -6349,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>San Lucas Tecopilco</t>
@@ -6362,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -6375,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -6388,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Tzompantepec</t>
@@ -6401,6 +8531,11 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -6414,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6445,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -6458,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Amatitlán</t>
@@ -6471,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Apazapan</t>
@@ -6480,13 +8635,18 @@
         <v>2</v>
       </c>
       <c r="D460">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Cazones de Herrera</t>
+          <t>Cazones De Herrera</t>
         </is>
       </c>
       <c r="C461">
@@ -6497,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -6510,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -6519,10 +8689,15 @@
         <v>2</v>
       </c>
       <c r="D463">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -6536,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -6549,9 +8729,14 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C466">
@@ -6562,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Coxquihui</t>
@@ -6575,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -6588,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Espinal</t>
@@ -6601,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -6614,19 +8819,29 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C471">
         <v>2</v>
       </c>
       <c r="D471">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -6640,9 +8855,14 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Sureste</t>
+          <t>Ixhuatlán Del Sureste</t>
         </is>
       </c>
       <c r="C473">
@@ -6653,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Ixmatlahuacan</t>
@@ -6666,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -6675,10 +8905,15 @@
         <v>2</v>
       </c>
       <c r="D475">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Jalcomulco</t>
@@ -6692,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Jamapa</t>
@@ -6705,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -6718,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -6731,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -6744,9 +8999,14 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C481">
@@ -6757,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Mecayapan</t>
@@ -6770,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -6783,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -6796,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -6805,10 +9085,15 @@
         <v>2</v>
       </c>
       <c r="D485">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -6822,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -6831,13 +9121,18 @@
         <v>2</v>
       </c>
       <c r="D487">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Paso del Macho</t>
+          <t>Paso Del Macho</t>
         </is>
       </c>
       <c r="C488">
@@ -6848,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -6861,9 +9161,14 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C490">
@@ -6874,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -6883,10 +9193,15 @@
         <v>2</v>
       </c>
       <c r="D491">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -6900,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -6909,13 +9229,18 @@
         <v>2</v>
       </c>
       <c r="D493">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C494">
@@ -6926,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Tantoyuca</t>
@@ -6939,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -6948,10 +9283,15 @@
         <v>2</v>
       </c>
       <c r="D496">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -6965,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Tlacotalpan</t>
@@ -6978,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -6991,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -7004,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -7017,6 +9377,11 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -7026,10 +9391,15 @@
         <v>2</v>
       </c>
       <c r="D502">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -7043,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -7056,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -7069,6 +9449,11 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -7082,6 +9467,11 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7113,6 +9503,11 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7144,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -7157,6 +9557,11 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -7166,10 +9571,15 @@
         <v>2</v>
       </c>
       <c r="D512">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -7183,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7192,7 +9607,7 @@
         <v>20</v>
       </c>
       <c r="D514">
-        <v>0.009237875288683603</v>
+        <v>0.009237875288683604</v>
       </c>
     </row>
     <row r="515">
@@ -7206,41 +9621,6 @@
       </c>
       <c r="D515">
         <v>1</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
